--- a/thong so.xlsx
+++ b/thong so.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="monter" sheetId="1" r:id="rId1"/>
-    <sheet name="hero" sheetId="2" r:id="rId2"/>
+    <sheet name="monter_skeleton" sheetId="3" r:id="rId1"/>
+    <sheet name="monter_thief" sheetId="1" r:id="rId2"/>
+    <sheet name="hero" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="35">
   <si>
     <t>Attack Physic</t>
   </si>
@@ -120,6 +121,21 @@
   </si>
   <si>
     <t>Full Area</t>
+  </si>
+  <si>
+    <t>skeleton_sword</t>
+  </si>
+  <si>
+    <t>skeleton_bow</t>
+  </si>
+  <si>
+    <t>skeleton_mage</t>
+  </si>
+  <si>
+    <t>skeleton_warlock</t>
+  </si>
+  <si>
+    <t>skeleton_knight</t>
   </si>
 </sst>
 </file>
@@ -223,12 +239,15 @@
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -244,9 +263,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -263,6 +279,3137 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>HP</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>monter_skeleton!$A$1:$B$33</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>monter_skeleton!$A$3:$B$3</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="1"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>HP</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl/>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>monter_skeleton!$C$1:$C$33</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>monter_skeleton!$C$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BF45-428A-A9A6-64A8C9468FAD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1261310511"/>
+        <c:axId val="1261313007"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_skeleton!$A$1:$B$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>monter_skeleton!$A$3:$B$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:multiLvlStrCache>
+                      <c:ptCount val="1"/>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl/>
+                    </c:multiLvlStrCache>
+                  </c:multiLvlStrRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_skeleton!$D$1:$D$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>monter_skeleton!$D$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="1"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-BF45-428A-A9A6-64A8C9468FAD}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent3"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_skeleton!$A$1:$B$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>monter_skeleton!$A$3:$B$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:multiLvlStrCache>
+                      <c:ptCount val="1"/>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl/>
+                    </c:multiLvlStrCache>
+                  </c:multiLvlStrRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_skeleton!$E$1:$E$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>monter_skeleton!$E$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-BF45-428A-A9A6-64A8C9468FAD}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="3"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent4"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_skeleton!$A$1:$B$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>monter_skeleton!$A$3:$B$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:multiLvlStrCache>
+                      <c:ptCount val="1"/>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl/>
+                    </c:multiLvlStrCache>
+                  </c:multiLvlStrRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_skeleton!$F$1:$F$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>monter_skeleton!$F$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>0.2</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-BF45-428A-A9A6-64A8C9468FAD}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="4"/>
+                <c:order val="4"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent5"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_skeleton!$A$1:$B$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>monter_skeleton!$A$3:$B$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:multiLvlStrCache>
+                      <c:ptCount val="1"/>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl/>
+                    </c:multiLvlStrCache>
+                  </c:multiLvlStrRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_skeleton!$G$1:$G$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>monter_skeleton!$G$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="1"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000004-BF45-428A-A9A6-64A8C9468FAD}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="5"/>
+                <c:order val="5"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent6"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_skeleton!$A$1:$B$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>monter_skeleton!$A$3:$B$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:multiLvlStrCache>
+                      <c:ptCount val="1"/>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl/>
+                    </c:multiLvlStrCache>
+                  </c:multiLvlStrRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_skeleton!$H$1:$H$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>monter_skeleton!$H$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="1"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000005-BF45-428A-A9A6-64A8C9468FAD}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1261310511"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1261313007"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1261313007"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1261310511"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>HP</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>monter_thief!$A$1:$B$33</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(monter_thief!$A$3:$B$3,monter_thief!$A$10:$B$10,monter_thief!$A$17:$B$17,monter_thief!$A$24:$B$24,monter_thief!$A$31:$B$31)</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="5"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>HP</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>HP</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>HP</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>HP</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>HP</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl/>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>monter_thief!$C$1:$C$33</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(monter_thief!$C$3,monter_thief!$C$10,monter_thief!$C$17,monter_thief!$C$24,monter_thief!$C$31)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>700</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D6B2-4F06-A5D3-90C646475992}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1261310511"/>
+        <c:axId val="1261313007"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:layout/>
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_thief!$A$1:$B$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>(monter_thief!$A$3:$B$3,monter_thief!$A$10:$B$10,monter_thief!$A$17:$B$17,monter_thief!$A$24:$B$24,monter_thief!$A$31:$B$31)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:multiLvlStrCache>
+                      <c:ptCount val="5"/>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="4">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl/>
+                    </c:multiLvlStrCache>
+                  </c:multiLvlStrRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_thief!$D$1:$D$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>(monter_thief!$D$3,monter_thief!$D$10,monter_thief!$D$17,monter_thief!$D$24,monter_thief!$D$31)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="5"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-D6B2-4F06-A5D3-90C646475992}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent3"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:layout/>
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_thief!$A$1:$B$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>(monter_thief!$A$3:$B$3,monter_thief!$A$10:$B$10,monter_thief!$A$17:$B$17,monter_thief!$A$24:$B$24,monter_thief!$A$31:$B$31)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:multiLvlStrCache>
+                      <c:ptCount val="5"/>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="4">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl/>
+                    </c:multiLvlStrCache>
+                  </c:multiLvlStrRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_thief!$E$1:$E$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>(monter_thief!$E$3,monter_thief!$E$10,monter_thief!$E$17,monter_thief!$E$24,monter_thief!$E$31)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="5"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>0</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-D6B2-4F06-A5D3-90C646475992}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="3"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent4"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:layout/>
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_thief!$A$1:$B$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>(monter_thief!$A$3:$B$3,monter_thief!$A$10:$B$10,monter_thief!$A$17:$B$17,monter_thief!$A$24:$B$24,monter_thief!$A$31:$B$31)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:multiLvlStrCache>
+                      <c:ptCount val="5"/>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="4">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl/>
+                    </c:multiLvlStrCache>
+                  </c:multiLvlStrRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_thief!$F$1:$F$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>(monter_thief!$F$3,monter_thief!$F$10,monter_thief!$F$17,monter_thief!$F$24,monter_thief!$F$31)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="5"/>
+                      <c:pt idx="0">
+                        <c:v>0.2</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>0.2</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0.2</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>0.2</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>0.2</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-D6B2-4F06-A5D3-90C646475992}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="4"/>
+                <c:order val="4"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent5"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:layout/>
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_thief!$A$1:$B$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>(monter_thief!$A$3:$B$3,monter_thief!$A$10:$B$10,monter_thief!$A$17:$B$17,monter_thief!$A$24:$B$24,monter_thief!$A$31:$B$31)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:multiLvlStrCache>
+                      <c:ptCount val="5"/>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="4">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl/>
+                    </c:multiLvlStrCache>
+                  </c:multiLvlStrRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_thief!$G$1:$G$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>(monter_thief!$G$3,monter_thief!$G$10,monter_thief!$G$17,monter_thief!$G$24,monter_thief!$G$31)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="5"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000004-D6B2-4F06-A5D3-90C646475992}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="5"/>
+                <c:order val="5"/>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent6"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:layout/>
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:multiLvlStrRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_thief!$A$1:$B$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>(monter_thief!$A$3:$B$3,monter_thief!$A$10:$B$10,monter_thief!$A$17:$B$17,monter_thief!$A$24:$B$24,monter_thief!$A$31:$B$31)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:multiLvlStrCache>
+                      <c:ptCount val="5"/>
+                      <c:lvl>
+                        <c:pt idx="0">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="1">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="2">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="3">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                        <c:pt idx="4">
+                          <c:v>HP</c:v>
+                        </c:pt>
+                      </c:lvl>
+                      <c:lvl/>
+                    </c:multiLvlStrCache>
+                  </c:multiLvlStrRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>monter_thief!$H$1:$H$33</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>(monter_thief!$H$3,monter_thief!$H$10,monter_thief!$H$17,monter_thief!$H$24,monter_thief!$H$31)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="5"/>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000005-D6B2-4F06-A5D3-90C646475992}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1261310511"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1261313007"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1261313007"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1261310511"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>585787</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>280987</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -540,448 +3687,919 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2">
+      <c r="C1" s="1">
         <v>30</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="4">
         <v>1.2</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="4">
         <f>C1*(30/F2)*F4</f>
         <v>750</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2">
-        <v>800</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="3" t="s">
+      <c r="C3" s="1">
+        <v>1000</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>0.2</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2">
-        <v>5</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="3" t="s">
+      <c r="C4" s="1">
+        <v>7</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="2">
-        <v>5</v>
-      </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="C5" s="1">
+        <v>7</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>20</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="1">
         <v>5</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="9">
-        <v>1</v>
-      </c>
-      <c r="G9" s="9" t="s">
+      <c r="F9" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="4">
         <f>C8*(30/F9)*F11</f>
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>800</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="3" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>0.2</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="1">
         <v>5</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="3" t="s">
+      <c r="D11" s="8"/>
+      <c r="E11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>1</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <v>5</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="2">
-        <v>15</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="C15" s="1">
+        <v>5</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="1">
+        <v>20</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="4">
+        <f>C16*(30/F16)*F18</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1">
+        <v>800</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="C18" s="1">
+        <v>5</v>
+      </c>
+      <c r="D18" s="8"/>
+      <c r="E18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1">
+        <v>5</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1">
+        <v>5</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1">
+        <v>30</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="4">
+        <f>C23*(30/F23)*F25</f>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1">
+        <v>900</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="1">
+        <v>5</v>
+      </c>
+      <c r="D25" s="8"/>
+      <c r="E25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1">
+        <v>5</v>
+      </c>
+      <c r="D26" s="8"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1">
+        <v>35</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="1">
+        <v>5</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="4">
+        <f>C29*(30/F30)*F32</f>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1500</v>
+      </c>
+      <c r="D31" s="8"/>
+      <c r="E31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="1">
+        <v>15</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1">
+        <v>15</v>
+      </c>
+      <c r="D33" s="8"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="D16:D19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="37.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1">
+        <v>30</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7"/>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>5</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4">
+        <f>C1*(30/F2)*F4</f>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="7"/>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1">
+        <v>800</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1">
+        <v>5</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1">
+        <v>5</v>
+      </c>
+      <c r="D5" s="11"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1">
+        <v>20</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+      <c r="B9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>5</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F9" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="4">
+        <f>C8*(30/F9)*F11</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+      <c r="B10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="1">
+        <v>800</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="2">
         <v>1</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="7"/>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1">
+        <v>5</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
         <v>15</v>
       </c>
-      <c r="H16" s="9">
+      <c r="D15" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="B16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="4">
         <f>C15*(30/F16)*F18</f>
         <v>450</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="7"/>
+      <c r="B17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="1">
         <v>1200</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="3" t="s">
+      <c r="D17" s="8"/>
+      <c r="E17" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <v>0.2</v>
       </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="2" t="s">
+      <c r="A18" s="7"/>
+      <c r="B18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="1">
         <v>10</v>
       </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="3" t="s">
+      <c r="D18" s="8"/>
+      <c r="E18" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <v>1</v>
       </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="2" t="s">
+      <c r="A19" s="7"/>
+      <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="1">
         <v>10</v>
       </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="1">
         <v>10</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="2" t="s">
+      <c r="A23" s="7"/>
+      <c r="B23" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="1">
         <v>5</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="4">
         <v>1</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="4">
         <f>C22*(30/F23)*F25</f>
         <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="2" t="s">
+      <c r="A24" s="7"/>
+      <c r="B24" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="1">
         <v>1100</v>
       </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="3" t="s">
+      <c r="D24" s="8"/>
+      <c r="E24" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="2">
         <v>0.2</v>
       </c>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="2" t="s">
+      <c r="A25" s="7"/>
+      <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="1">
         <v>7</v>
       </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="3" t="s">
+      <c r="D25" s="8"/>
+      <c r="E25" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="2">
         <v>1</v>
       </c>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="2" t="s">
+      <c r="A26" s="7"/>
+      <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="1">
         <v>7</v>
       </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="1">
         <v>5</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="2" t="s">
+      <c r="A30" s="7"/>
+      <c r="B30" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="1">
         <v>35</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="4">
         <v>1.5</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="4">
         <f>C30*(30/F30)*F32</f>
         <v>1050</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="2" t="s">
+      <c r="A31" s="7"/>
+      <c r="B31" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="1">
         <v>700</v>
       </c>
-      <c r="D31" s="5"/>
-      <c r="E31" s="3" t="s">
+      <c r="D31" s="8"/>
+      <c r="E31" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="2">
         <v>0.2</v>
       </c>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="2" t="s">
+      <c r="A32" s="7"/>
+      <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="1">
         <v>5</v>
       </c>
-      <c r="D32" s="5"/>
-      <c r="E32" s="3" t="s">
+      <c r="D32" s="8"/>
+      <c r="E32" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
         <v>1.5</v>
       </c>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="2" t="s">
+      <c r="A33" s="7"/>
+      <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="1">
         <v>5</v>
       </c>
-      <c r="D33" s="5"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -998,10 +4616,11 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1015,380 +4634,380 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2">
+      <c r="C1" s="1">
         <v>20</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="7"/>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="4">
         <v>3</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="4">
         <f>C1*(30/F2)*F4</f>
         <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>1200</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="10"/>
+      <c r="E3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>0.2</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="7"/>
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>200</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="3" t="s">
+      <c r="D4" s="10"/>
+      <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="7"/>
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>10</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="D5" s="10"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>10</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>2</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="1">
         <v>20</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="4">
         <v>2</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="4">
         <f>C11*(30/F11)*F13</f>
         <v>300</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="4">
         <v>10</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="M11" s="9">
+      <c r="M11" s="4">
         <f>((C11*K13)+K16)*K14</f>
         <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2" t="s">
+      <c r="A12" s="7"/>
+      <c r="B12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="1">
         <v>1200</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="3" t="s">
+      <c r="D12" s="10"/>
+      <c r="E12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>0.2</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="3" t="s">
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="2">
         <v>5</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="L12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="2">
         <f>M11*K15</f>
         <v>1200</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="2" t="s">
+      <c r="A13" s="7"/>
+      <c r="B13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <v>200</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="3" t="s">
+      <c r="D13" s="10"/>
+      <c r="E13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>1</v>
       </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="3" t="s">
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="2">
         <v>1</v>
       </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="2" t="s">
+      <c r="A14" s="7"/>
+      <c r="B14" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="1">
         <v>5</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="3" t="s">
+      <c r="D14" s="10"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="5">
         <v>3</v>
       </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="7"/>
+      <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="1">
         <v>5</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="3" t="s">
+      <c r="D15" s="11"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="2">
         <v>4</v>
       </c>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J16" s="11" t="s">
+      <c r="J16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K16" s="11">
+      <c r="K16" s="6">
         <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="1">
         <v>2</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="2" t="s">
+      <c r="A20" s="7"/>
+      <c r="B20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="1">
         <v>20</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="4">
         <v>2</v>
       </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="2" t="s">
+      <c r="A21" s="7"/>
+      <c r="B21" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <v>1200</v>
       </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="3" t="s">
+      <c r="D21" s="10"/>
+      <c r="E21" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
         <v>0.2</v>
       </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="2" t="s">
+      <c r="A22" s="7"/>
+      <c r="B22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="1">
         <v>200</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="3" t="s">
+      <c r="D22" s="10"/>
+      <c r="E22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="2">
         <v>1</v>
       </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="2" t="s">
+      <c r="A23" s="7"/>
+      <c r="B23" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="1">
         <v>5</v>
       </c>
-      <c r="D23" s="7"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+      <c r="D23" s="10"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="2" t="s">
+      <c r="A24" s="7"/>
+      <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="1">
         <v>5</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A19:A24"/>
+    <mergeCell ref="D20:D24"/>
     <mergeCell ref="I11:I15"/>
     <mergeCell ref="A1:A6"/>
     <mergeCell ref="D2:D6"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="D11:D15"/>
-    <mergeCell ref="A19:A24"/>
-    <mergeCell ref="D20:D24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
